--- a/assets/templates/Pelawat.xlsx
+++ b/assets/templates/Pelawat.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView activeTab="3" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="600" visibility="visible"/>
+    <workbookView activeTab="11" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="600" visibility="visible"/>
   </bookViews>
   <sheets>
     <sheet name="JANUARI" sheetId="1" r:id="rId4"/>
@@ -96,7 +96,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <b val="0"/>
       <i val="0"/>
@@ -119,6 +119,15 @@
     </font>
     <font>
       <b val="0"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
+      <sz val="26"/>
+      <color theme="1"/>
+      <name val="Bernard MT Condensed"/>
+    </font>
+    <font>
+      <b val="1"/>
       <i val="0"/>
       <strike val="0"/>
       <u val="none"/>
@@ -258,7 +267,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
@@ -319,6 +328,12 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="9" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
+    <xf xfId="0" fontId="3" numFmtId="0" fillId="0" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="3" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -668,7 +683,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" customHeight="1" ht="32.25">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="19"/>
@@ -1293,7 +1308,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" customHeight="1" ht="32.25">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="23" t="s">
         <v>18</v>
       </c>
       <c r="B1" s="20"/>
@@ -1919,7 +1934,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" customHeight="1" ht="32.25">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="23" t="s">
         <v>19</v>
       </c>
       <c r="B1" s="20"/>
@@ -2543,7 +2558,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" customHeight="1" ht="32.25">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="23" t="s">
         <v>20</v>
       </c>
       <c r="B1" s="20"/>
@@ -3166,7 +3181,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" customHeight="1" ht="32.25">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="22" t="s">
         <v>10</v>
       </c>
       <c r="B1" s="19"/>
@@ -3789,7 +3804,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" customHeight="1" ht="32.25">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="22" t="s">
         <v>11</v>
       </c>
       <c r="B1" s="19"/>
@@ -4412,7 +4427,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" customHeight="1" ht="32.25">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="22" t="s">
         <v>12</v>
       </c>
       <c r="B1" s="19"/>
@@ -5035,7 +5050,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" customHeight="1" ht="32.25">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="22" t="s">
         <v>13</v>
       </c>
       <c r="B1" s="19"/>
@@ -5658,7 +5673,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" customHeight="1" ht="32.25">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="22" t="s">
         <v>14</v>
       </c>
       <c r="B1" s="19"/>
@@ -6281,7 +6296,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" customHeight="1" ht="32.25">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="23" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="20"/>
@@ -6904,7 +6919,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" customHeight="1" ht="32.25">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="23" t="s">
         <v>16</v>
       </c>
       <c r="B1" s="20"/>
@@ -7529,7 +7544,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" customHeight="1" ht="32.25">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="23" t="s">
         <v>17</v>
       </c>
       <c r="B1" s="20"/>

--- a/assets/templates/Pelawat.xlsx
+++ b/assets/templates/Pelawat.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView activeTab="11" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="600" visibility="visible"/>
+    <workbookView activeTab="3" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="600" visibility="visible"/>
   </bookViews>
   <sheets>
     <sheet name="JANUARI" sheetId="1" r:id="rId4"/>
@@ -96,7 +96,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <b val="0"/>
       <i val="0"/>
@@ -119,15 +119,6 @@
     </font>
     <font>
       <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
-      <sz val="26"/>
-      <color theme="1"/>
-      <name val="Bernard MT Condensed"/>
-    </font>
-    <font>
-      <b val="1"/>
       <i val="0"/>
       <strike val="0"/>
       <u val="none"/>
@@ -267,7 +258,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="22">
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
@@ -328,12 +319,6 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="9" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
-    <xf xfId="0" fontId="3" numFmtId="0" fillId="0" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="3" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -683,7 +668,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" customHeight="1" ht="32.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="19"/>
@@ -1308,7 +1293,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" customHeight="1" ht="32.25">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="20" t="s">
         <v>18</v>
       </c>
       <c r="B1" s="20"/>
@@ -1934,7 +1919,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" customHeight="1" ht="32.25">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="20" t="s">
         <v>19</v>
       </c>
       <c r="B1" s="20"/>
@@ -2558,7 +2543,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" customHeight="1" ht="32.25">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="20" t="s">
         <v>20</v>
       </c>
       <c r="B1" s="20"/>
@@ -3181,7 +3166,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" customHeight="1" ht="32.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="19" t="s">
         <v>10</v>
       </c>
       <c r="B1" s="19"/>
@@ -3804,7 +3789,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" customHeight="1" ht="32.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="19" t="s">
         <v>11</v>
       </c>
       <c r="B1" s="19"/>
@@ -4427,7 +4412,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" customHeight="1" ht="32.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="19" t="s">
         <v>12</v>
       </c>
       <c r="B1" s="19"/>
@@ -5050,7 +5035,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" customHeight="1" ht="32.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="19" t="s">
         <v>13</v>
       </c>
       <c r="B1" s="19"/>
@@ -5673,7 +5658,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" customHeight="1" ht="32.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="19" t="s">
         <v>14</v>
       </c>
       <c r="B1" s="19"/>
@@ -6296,7 +6281,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" customHeight="1" ht="32.25">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="20" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="20"/>
@@ -6919,7 +6904,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" customHeight="1" ht="32.25">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="20" t="s">
         <v>16</v>
       </c>
       <c r="B1" s="20"/>
@@ -7544,7 +7529,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" customHeight="1" ht="32.25">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="20" t="s">
         <v>17</v>
       </c>
       <c r="B1" s="20"/>

--- a/assets/templates/Pelawat.xlsx
+++ b/assets/templates/Pelawat.xlsx
@@ -118,13 +118,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
       <sz val="26"/>
       <color theme="1"/>
       <name val="Bernard MT Condensed"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -318,7 +315,9 @@
     <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="9" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="9" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
